--- a/Espanha - Danuta/PlanejamentoV1.xlsx
+++ b/Espanha - Danuta/PlanejamentoV1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Arquivos Pessoais\Viagens\20250912 - Valencia_Lisboa\Espanha - Danuta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E41E2D6A-CEE1-4424-B775-78F199934BF4}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54846409-F4C3-44EF-B726-3A37717EC8EB}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{EE7FA94F-19AC-487D-8C3A-419B2AA33447}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="60">
   <si>
     <t>Data</t>
   </si>
@@ -108,39 +108,10 @@
     <t>Hotel</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Ibis Murcia</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-Endereço: Madre Paula Gil Cano, s/n, 30009 Múrcia, Espanha
-Telefone: +34 968 27 49 39
-Coordenadas para GPS: N 038° 0.144, W 01° 8.570</t>
-    </r>
-  </si>
-  <si>
     <t>A fazer</t>
   </si>
   <si>
     <t>Planejamento</t>
-  </si>
-  <si>
-    <t>Voltar para valencia - Inicio das Aulas</t>
   </si>
   <si>
     <t>KM</t>
@@ -230,6 +201,12 @@
     </r>
   </si>
   <si>
+    <t xml:space="preserve">Dorme em </t>
+  </si>
+  <si>
+    <t>Almeria</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <b/>
@@ -239,7 +216,33 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>Hotel Presidente</t>
+      <t>Ibis Murcia (26 e 27 de agosto)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Endereço: Madre Paula Gil Cano, s/n, 30009 Múrcia, Espanha
+Telefone: +34 968 27 49 39
+Coordenadas para GPS: N 038° 0.144, W 01° 8.570</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Hotel Presidente (27 a 30 de agosto)</t>
     </r>
     <r>
       <rPr>
@@ -256,29 +259,110 @@
     </r>
   </si>
   <si>
-    <t>Calnegue / Gramita</t>
-  </si>
-  <si>
-    <t>Em aberto a parte da tarde</t>
-  </si>
-  <si>
-    <t>Raja / Carral</t>
-  </si>
-  <si>
-    <t>Cala Alambrad</t>
-  </si>
-  <si>
-    <t>Gandia (pela manhã)</t>
+    <t>A ver</t>
+  </si>
+  <si>
+    <t>Cartagena</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Pedro Jover 9 R&amp;R (30 de agosto a 01 de setembro)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Endereço: 9 Calle Pedro Jover 1º B, 04002 Almeria,
+Espanha
+Telefone: +34 620 91 79 97
+Coordenadas para GPS: N 036° 50.251, W 02°
+28.184</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Piso a 3 minutos de la playa (01 e 02 de setembro)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Endereço: Calle Cardenal Belluga, 2 2º C, 30860 Puerto
+de Mazarrón, Espanha
+Telefone: +34 630 70 98 46
+Coordenadas para GPS: N 037° 34.174, W 01° 15.499</t>
+    </r>
+  </si>
+  <si>
+    <t>Puerto de Mazarron</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Sercotel Carlos III (02 e 03 de setembro)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Endereço: Carlos III, 49, 30201
+Cartagena, Espanha
+Telefone: +34 968 52 00 32
+Coordenadas para GPS: N 037°
+36.359, W 00° 58.951</t>
+    </r>
+  </si>
+  <si>
+    <t>Valencia - Aula Clara</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
+    <numFmt numFmtId="44" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -307,6 +391,13 @@
       <b/>
       <i/>
       <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -345,7 +436,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -419,39 +510,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
@@ -461,10 +519,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -508,21 +567,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -532,6 +582,31 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="44" fontId="1" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -544,35 +619,22 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Moeda" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -965,10 +1027,10 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="23" t="s">
+      <c r="B1" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="24"/>
+      <c r="C1" s="30"/>
       <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
@@ -1208,30 +1270,30 @@
   <cols>
     <col min="1" max="1" width="39.5703125" style="11" customWidth="1"/>
     <col min="2" max="2" width="42.28515625" style="3" customWidth="1"/>
-    <col min="3" max="4" width="9.140625" style="22"/>
+    <col min="3" max="4" width="9.140625" style="19"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="31" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="26" t="s">
-        <v>30</v>
-      </c>
-      <c r="D1" s="26" t="s">
-        <v>31</v>
+      <c r="B1" s="31"/>
+      <c r="C1" s="32" t="s">
+        <v>28</v>
+      </c>
+      <c r="D1" s="32" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="16" t="s">
+      <c r="A2" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="B2" s="16" t="s">
+      <c r="B2" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="C2" s="26"/>
-      <c r="D2" s="26"/>
+      <c r="C2" s="32"/>
+      <c r="D2" s="32"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
@@ -1240,10 +1302,10 @@
       <c r="B3" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="C3" s="20">
+      <c r="C3" s="17">
         <v>217</v>
       </c>
-      <c r="D3" s="21">
+      <c r="D3" s="18">
         <v>0.10416666666666667</v>
       </c>
     </row>
@@ -1253,13 +1315,13 @@
         <v>Murcia</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="C4" s="20">
+        <v>30</v>
+      </c>
+      <c r="C4" s="17">
         <v>52</v>
       </c>
-      <c r="D4" s="20" t="s">
-        <v>33</v>
+      <c r="D4" s="17" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -1268,13 +1330,13 @@
         <v>Totana</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="C5" s="20">
+        <v>32</v>
+      </c>
+      <c r="C5" s="17">
         <v>35</v>
       </c>
-      <c r="D5" s="20" t="s">
-        <v>35</v>
+      <c r="D5" s="17" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="30" x14ac:dyDescent="0.25">
@@ -1283,13 +1345,13 @@
         <v>Ermita Ramonete, 30876, Murcia, Espanha</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="C6" s="20">
+        <v>34</v>
+      </c>
+      <c r="C6" s="17">
         <v>24</v>
       </c>
-      <c r="D6" s="20" t="s">
-        <v>37</v>
+      <c r="D6" s="17" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="30" x14ac:dyDescent="0.25">
@@ -1298,13 +1360,13 @@
         <v>Club playa grande, Calle de babor (playa grande), 30870, Murcia, Espanha</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="C7" s="20">
+        <v>36</v>
+      </c>
+      <c r="C7" s="17">
         <v>30</v>
       </c>
-      <c r="D7" s="20" t="s">
-        <v>39</v>
+      <c r="D7" s="17" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="30" x14ac:dyDescent="0.25">
@@ -1313,12 +1375,12 @@
         <v>Puntas de Calnegre, 30876, Murcia, Espanha</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="C8" s="20">
+        <v>38</v>
+      </c>
+      <c r="C8" s="17">
         <v>264</v>
       </c>
-      <c r="D8" s="21">
+      <c r="D8" s="18">
         <v>0.12361111111111112</v>
       </c>
     </row>
@@ -1328,12 +1390,12 @@
         <v>Granada, Espanha</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="C9" s="20">
+        <v>39</v>
+      </c>
+      <c r="C9" s="17">
         <v>150</v>
       </c>
-      <c r="D9" s="21">
+      <c r="D9" s="18">
         <v>6.9444444444444434E-2</v>
       </c>
     </row>
@@ -1343,12 +1405,12 @@
         <v>Málaga, Espanha</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="C10" s="20">
+        <v>40</v>
+      </c>
+      <c r="C10" s="17">
         <v>135</v>
       </c>
-      <c r="D10" s="21">
+      <c r="D10" s="18">
         <v>7.013888888888889E-2</v>
       </c>
     </row>
@@ -1358,12 +1420,12 @@
         <v>Ronda, 29400, Málaga, Espanha</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="C11" s="20">
+        <v>41</v>
+      </c>
+      <c r="C11" s="17">
         <v>161</v>
       </c>
-      <c r="D11" s="21">
+      <c r="D11" s="18">
         <v>7.9166666666666663E-2</v>
       </c>
     </row>
@@ -1373,12 +1435,12 @@
         <v>Nerja, 29780, Málaga, Espanha</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="C12" s="20">
+        <v>42</v>
+      </c>
+      <c r="C12" s="17">
         <v>247</v>
       </c>
-      <c r="D12" s="21">
+      <c r="D12" s="18">
         <v>0.12291666666666667</v>
       </c>
     </row>
@@ -1388,12 +1450,12 @@
         <v>Carboneras, Almería, Espanha</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="C13" s="20">
+        <v>43</v>
+      </c>
+      <c r="C13" s="17">
         <v>150</v>
       </c>
-      <c r="D13" s="21">
+      <c r="D13" s="18">
         <v>6.5972222222222224E-2</v>
       </c>
     </row>
@@ -1403,12 +1465,12 @@
         <v>Mazarrón, Murcia, Espanha</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="C14" s="20">
+        <v>44</v>
+      </c>
+      <c r="C14" s="17">
         <v>115</v>
       </c>
-      <c r="D14" s="21">
+      <c r="D14" s="18">
         <v>5.5555555555555552E-2</v>
       </c>
     </row>
@@ -1418,12 +1480,12 @@
         <v>Torrevieja, Alicante, Espanha</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="C15" s="20">
+        <v>45</v>
+      </c>
+      <c r="C15" s="17">
         <v>110</v>
       </c>
-      <c r="D15" s="21">
+      <c r="D15" s="18">
         <v>5.4166666666666669E-2</v>
       </c>
     </row>
@@ -1433,13 +1495,13 @@
         <v>Cala Almadraba, Mar Mediterráneo, 03503, Alicante, Espanha</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="C16" s="20">
+        <v>46</v>
+      </c>
+      <c r="C16" s="17">
         <v>75</v>
       </c>
-      <c r="D16" s="20" t="s">
-        <v>49</v>
+      <c r="D16" s="17" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -1450,21 +1512,21 @@
       <c r="B17" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="C17" s="20">
+      <c r="C17" s="17">
         <v>75</v>
       </c>
-      <c r="D17" s="21">
+      <c r="D17" s="18">
         <v>4.7222222222222221E-2</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="2"/>
       <c r="B18" s="7"/>
-      <c r="C18" s="20">
+      <c r="C18" s="17">
         <f>SUM(C3:C17)</f>
         <v>1840</v>
       </c>
-      <c r="D18" s="20"/>
+      <c r="D18" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -1478,44 +1540,59 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0ACE9EE9-CEA7-48D8-907D-1B27326C0FD6}">
-  <dimension ref="A1:E23"/>
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="45.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="39.5703125" style="11" customWidth="1"/>
-    <col min="3" max="3" width="42.28515625" style="3" customWidth="1"/>
-    <col min="4" max="4" width="58.140625" style="3" customWidth="1"/>
-    <col min="5" max="5" width="48.7109375" customWidth="1"/>
+    <col min="1" max="1" width="43.85546875" customWidth="1"/>
+    <col min="2" max="2" width="18.7109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.28515625" style="23" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="55.140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="38.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.140625" style="28"/>
+    <col min="8" max="8" width="12.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="27" t="s">
-        <v>28</v>
-      </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
-      <c r="E1" s="27"/>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="16" t="s">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" s="31" t="s">
+        <v>27</v>
+      </c>
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="31"/>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="16" t="s">
+      <c r="B2" s="24" t="s">
         <v>22</v>
       </c>
-      <c r="C2" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="D2" s="16" t="s">
+      <c r="C2" s="24" t="s">
+        <v>49</v>
+      </c>
+      <c r="D2" s="20">
+        <f>SUM(D3:D10)</f>
+        <v>6927</v>
+      </c>
+      <c r="E2" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="E2" s="18" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" s="17" customFormat="1" ht="60" x14ac:dyDescent="0.25">
-      <c r="A3" s="28">
+      <c r="F2" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="H2" s="37">
+        <f>D2/2</f>
+        <v>3463.5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" s="16" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A3" s="25">
         <v>45895</v>
       </c>
       <c r="B3" s="7" t="s">
@@ -1524,193 +1601,177 @@
       <c r="C3" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="D3" s="7" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" s="17" customFormat="1" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="28">
+      <c r="D3" s="21">
+        <v>780</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="F3" s="26"/>
+      <c r="G3" s="28">
+        <v>9674</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" s="16" customFormat="1" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="25">
         <v>45896</v>
       </c>
       <c r="B4" s="7" t="str">
         <f>C3</f>
         <v>Murcia</v>
       </c>
-      <c r="C4" s="29" t="s">
+      <c r="C4" s="34" t="s">
         <v>6</v>
       </c>
-      <c r="D4" s="32" t="s">
-        <v>51</v>
-      </c>
-      <c r="E4" s="35" t="s">
+      <c r="D4" s="36">
+        <v>1857</v>
+      </c>
+      <c r="E4" s="34" t="s">
+        <v>52</v>
+      </c>
+      <c r="F4" s="34" t="s">
+        <v>48</v>
+      </c>
+      <c r="G4" s="33">
+        <v>9674</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" s="16" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A5" s="25">
+        <v>45897</v>
+      </c>
+      <c r="B5" s="34" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="34"/>
+      <c r="D5" s="36"/>
+      <c r="E5" s="34"/>
+      <c r="F5" s="34"/>
+      <c r="G5" s="33"/>
+    </row>
+    <row r="6" spans="1:8" s="16" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A6" s="25">
+        <v>45898</v>
+      </c>
+      <c r="B6" s="34"/>
+      <c r="C6" s="34"/>
+      <c r="D6" s="36"/>
+      <c r="E6" s="34"/>
+      <c r="F6" s="34"/>
+      <c r="G6" s="33"/>
+    </row>
+    <row r="7" spans="1:8" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="25">
+        <v>45899</v>
+      </c>
+      <c r="B7" s="34"/>
+      <c r="C7" s="7" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" s="17" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A5" s="28">
-        <v>45897</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" s="30"/>
-      <c r="D5" s="33"/>
-      <c r="E5" s="35"/>
-    </row>
-    <row r="6" spans="1:5" s="17" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="28">
-        <v>45898</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C6" s="31"/>
-      <c r="D6" s="34"/>
-      <c r="E6" s="35"/>
-    </row>
-    <row r="7" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="28">
-        <v>45899</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C7" s="6" t="s">
+      <c r="D7" s="36">
+        <f>2395</f>
+        <v>2395</v>
+      </c>
+      <c r="E7" s="35" t="s">
+        <v>55</v>
+      </c>
+      <c r="F7" s="27"/>
+      <c r="G7" s="33">
+        <v>9152</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="25">
+        <v>45900</v>
+      </c>
+      <c r="B8" s="7" t="str">
+        <f>C7</f>
+        <v>Almeria</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="D8" s="36"/>
+      <c r="E8" s="35"/>
+      <c r="F8" s="27"/>
+      <c r="G8" s="33"/>
+    </row>
+    <row r="9" spans="1:8" ht="75" x14ac:dyDescent="0.25">
+      <c r="A9" s="25">
+        <v>45901</v>
+      </c>
+      <c r="B9" s="7" t="str">
+        <f>C8</f>
+        <v>Almeria</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="D9" s="21">
+        <v>897</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="F9" s="27"/>
+      <c r="G9" s="28">
+        <v>9152</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="90" x14ac:dyDescent="0.25">
+      <c r="A10" s="25">
+        <v>45902</v>
+      </c>
+      <c r="B10" s="7" t="str">
+        <f>C9</f>
+        <v>Puerto de Mazarron</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="D10" s="21">
+        <v>998</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="F10" s="27"/>
+      <c r="G10" s="28">
+        <v>9152</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A11" s="25">
+        <v>45903</v>
+      </c>
+      <c r="B11" s="7" t="str">
+        <f>C10</f>
+        <v>Cartagena</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="D11" s="22"/>
+      <c r="E11" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="D7" s="6"/>
-    </row>
-    <row r="8" spans="1:5" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A8" s="28">
-        <v>45900</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="C8" s="6"/>
-      <c r="D8" s="6"/>
-    </row>
-    <row r="9" spans="1:5" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="28">
-        <v>45901</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-    </row>
-    <row r="10" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="28">
-        <v>45902</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="C10" s="7"/>
-      <c r="D10" s="7"/>
-    </row>
-    <row r="11" spans="1:5" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A11" s="28">
-        <v>45903</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="C11" s="6"/>
-      <c r="D11" s="6"/>
-    </row>
-    <row r="12" spans="1:5" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A12" s="28">
-        <v>45904</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C12" s="7"/>
-      <c r="D12" s="7"/>
-    </row>
-    <row r="13" spans="1:5" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A13" s="28">
-        <v>45905</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C13" s="7"/>
-      <c r="D13" s="7"/>
-    </row>
-    <row r="14" spans="1:5" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A14" s="28">
-        <v>45906</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="D14" s="7"/>
-    </row>
-    <row r="15" spans="1:5" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A15" s="28"/>
-      <c r="B15" s="6"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="7"/>
-    </row>
-    <row r="16" spans="1:5" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A16" s="28"/>
-      <c r="B16" s="6"/>
-      <c r="C16" s="6"/>
-      <c r="D16" s="6"/>
-    </row>
-    <row r="17" spans="1:4" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A17" s="19"/>
-      <c r="B17" s="6"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="7"/>
-    </row>
-    <row r="18" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="19"/>
-      <c r="B18" s="6"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
-    </row>
-    <row r="19" spans="1:4" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A19" s="19"/>
-      <c r="B19" s="6"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
-    </row>
-    <row r="20" spans="1:4" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A20" s="19"/>
-      <c r="B20" s="2"/>
-      <c r="C20" s="15"/>
-    </row>
-    <row r="21" spans="1:4" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A21" s="19"/>
-      <c r="B21" s="6"/>
-      <c r="C21" s="7"/>
-    </row>
-    <row r="22" spans="1:4" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A22" s="19"/>
-      <c r="B22" s="6"/>
-      <c r="C22" s="7"/>
-    </row>
-    <row r="23" spans="1:4" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A23" s="19"/>
-      <c r="B23" s="6"/>
-      <c r="C23" s="7"/>
+      <c r="F11" s="27"/>
     </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A1:E1"/>
+  <mergeCells count="10">
+    <mergeCell ref="G7:G8"/>
+    <mergeCell ref="G4:G6"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="E4:E6"/>
+    <mergeCell ref="F4:F6"/>
+    <mergeCell ref="C4:C6"/>
+    <mergeCell ref="E7:E8"/>
+    <mergeCell ref="D7:D8"/>
     <mergeCell ref="D4:D6"/>
-    <mergeCell ref="E4:E6"/>
-    <mergeCell ref="C4:C6"/>
+    <mergeCell ref="B5:B7"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="72" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 
